--- a/www/download/IND.capital_depreciation.s.us.WIOD16.xlsx
+++ b/www/download/IND.capital_depreciation.s.us.WIOD16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96212.8130262516</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86730.0652467161</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>95507.6095032003</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121068.854393593</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>148204.660681268</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>169044.6419038</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179085.984396009</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>219178.994048912</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>233039.028476704</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>221368.292790303</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>268250.864051935</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>321046.074353054</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>341360.459426137</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>337502.905704562</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>323303.938161692</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54130.3194942804</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54839.3898492124</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59504.5973903603</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72912.8815972725</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83121.2999463737</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86385.9171911965</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90851.3951450564</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104034.932717279</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116519.985178344</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114935.981428721</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114305.599752088</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127250.449677056</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>120641.299931359</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>129241.022989831</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132901.935883639</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55377.9769319971</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56006.4490187792</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59355.4138687926</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74132.320621255</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85174.8579929179</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88057.2526818488</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92747.7405893125</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105902.386640807</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>119456.996667053</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110648.540541545</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>107648.038350102</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116712.115586673</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111187.830657806</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115795.786861816</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116889.181417221</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2954.68951752014</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3167.54238028317</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3508.7015736239</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4473.58635373867</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5104.20041151545</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6245.63278501954</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7305.98299938094</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9099.27008943847</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11909.2553537269</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12894.8876171913</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13089.5812753705</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15387.0058230541</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15178.8108997079</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16798.1629528367</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17181.0830873237</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136568.91374803</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>124503.298961399</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118602.942372533</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>131374.353364118</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>152697.953068857</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>192509.208520127</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218621.316036447</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>267128.724635167</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>333728.35823741</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>343250.794254708</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>437627.126192835</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>522355.458515737</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>516134.778250983</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>529004.873090277</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>559432.941714049</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87827.011993661</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86898.5075722408</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87952.5712539861</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100605.528277455</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113576.175459164</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129930.741764684</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149914.871078039</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177289.702079985</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>196786.047796662</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>185716.544021441</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>206054.303809858</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>224466.318235739</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>231398.065267077</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>242076.267540714</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>238014.222742558</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264950.425310826</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>290188.679716937</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>321703.083679771</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>385509.978489976</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>475640.452410863</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>574629.586415355</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>664895.750370545</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>773668.164135119</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>1061895.41132444</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1220596.43264076</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1485277.04892492</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1.883</t>
+          <t>1881714.61776087</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>2222783.29465165</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2.549</t>
+          <t>2550462.83095725</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2.847</t>
+          <t>2848717.49668251</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1964.08880112917</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1946.81343635922</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2163.61574791736</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2537.98256988878</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2884.63833589215</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2983.13242888441</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3420.26348162135</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3950.14463130369</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4807.2459472736</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4715.26220503201</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4847.8326884117</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5244.34556528486</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4869.90456949553</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5035.14178317727</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5334.50340825382</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25073.3873071619</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26777.9569435507</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31014.3964548787</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38067.1063868582</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43673.3475074377</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48784.427850061</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54304.9375703613</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66165.7954925089</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81920.0424372915</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74007.8717972692</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75343.3469081141</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83446.7404347647</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76532.0804784598</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77758.4768430917</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75602.5029978607</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>465839.897198338</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>467227.733196869</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>493053.207678929</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>588873.237895424</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>666485.895518307</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>685750.167935734</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>709482.452349357</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>812409.264259743</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>898814.491557332</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>859621.796065551</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>838763.761913679</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>901342.660239548</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>855681.902281266</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>907555.101401877</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>924829.864168098</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38334.2109255016</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39072.7560886336</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42138.0220816801</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51398.5574952465</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58347.4079533161</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60736.2429786984</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64503.8787533082</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75178.0499043001</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83175.367746906</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79553.4943680614</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80403.8000179726</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83788.3533798052</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78278.8534861239</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81199.192412883</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82770.468919583</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>99175.1890001269</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102905.999522474</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114192.805157306</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>147503.869650379</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179606.033801739</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>194950.993209483</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>217260.28230171</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>263183.625909465</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>309688.9159431</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>297988.796497027</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>312398.559633592</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>343068.703302047</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>323402.945907929</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>331446.970133385</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>336189.527003953</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>836.331991870257</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1014.81909280224</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1183.0270850575</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1663.28598387592</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2103.52580198109</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2385.14217948033</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2906.19241225523</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3882.82539955952</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4504.96102997144</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4265.15990848719</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4221.25242727729</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4666.98832348384</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4618.46893338651</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5410.87062228647</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5664.6538571414</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23081.3459039958</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23656.6666647379</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25029.7715820914</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30705.7398797858</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34981.5141766616</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36457.9969003658</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38314.6088594209</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44729.2853098203</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50804.8959451956</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51360.171521322</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49504.5875000285</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52988.2014326513</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51184.8404096611</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54187.0837068835</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55821.9442749734</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>226374.081285586</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>229768.994596295</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250773.774176741</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>312515.530678866</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>359407.244995</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>376826.423698733</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>400725.747924333</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>461528.053784302</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>515519.923242585</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>512417.548349397</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>518780.941763942</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>564185.582932056</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>538051.92174602</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>563525.237645964</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>570936.160677758</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>284243.912771875</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>279772.70715192</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>298331.53950808</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>337224.0130404</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>399064.481418067</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>426103.964552194</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>448137.065734683</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>516333.550848278</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>514769.828819693</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>454782.666284501</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>461695.755057696</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>495943.215658543</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>509786.331852085</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>527788.02353128</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>571114.313969117</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27498.0680600712</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28405.7394074023</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30291.1645184171</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32181.0252369924</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33771.0162357611</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36503.9498996808</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35671.0771920439</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41993.8572544497</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47908.6244343292</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48370.4796360053</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54751.8200827573</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53820.7182834728</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49928.3696860019</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50351.378700188</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51221.0701951072</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20883.9606121056</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21515.4563726258</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24321.2030480575</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30155.7364611995</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35152.5336673479</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36752.6750679954</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38426.596531965</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48643.7023392876</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55165.8502685804</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49542.6913689474</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50596.3521227293</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55055.6539272067</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51283.5925832792</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52933.641177849</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52130.7198318834</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47009.63222317</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43052.9773144481</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47889.7629920168</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56760.1890529227</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68309.9685858849</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72825.1028524078</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93682.5308605352</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108785.841892878</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>131244.700206299</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131661.531588079</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163862.076092308</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>191610.308481603</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>203278.245823974</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>192662.43029874</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>188264.133290177</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>111592.604905342</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111203.401998091</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>119983.431927393</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>144431.051884803</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>172939.295543881</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>203379.926192396</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>229953.397164111</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>289213.345619122</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>319533.675983194</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>329808.310568734</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>400585.340360796</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>451287.422374907</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>477076.540408715</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>506648.28987841</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>550059.622977075</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12547.7889183417</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13771.0262585835</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16370.7489364366</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20944.6098523364</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24996.9635008402</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30438.6620915976</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33008.0745036958</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36370.2560698647</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38981.1938231851</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47993.9602745445</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47428.651523775</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51918.9199359741</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48219.7407012542</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52120.4372519819</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58658.5927187914</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>200432.483795589</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>204291.456562131</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228417.54872117</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>281023.060194247</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>322758.324484707</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>337639.871728225</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>355743.557342027</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>407495.116942883</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>456595.942387498</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>455977.157012489</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>462667.013073372</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>503512.91320175</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>470186.405313954</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>484178.128296644</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>481118.712384928</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>1185138.49433602</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>1096647.11427096</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>1075989.48354226</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1184499.71263843</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.262</t>
+          <t>1255024.98469275</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>1231816.21756874</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>1178385.43123057</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1162996.69932027</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1323611.91537455</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1505242.51245923</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1647884.24854522</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1.784</t>
+          <t>1774831.98019559</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>1754750.47410304</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1371820.5073622</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1248641.36416907</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>178435.724608901</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>168729.545872359</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>188398.936279077</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>209259.545959891</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>240891.025580576</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>287559.157230581</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>337776.361539458</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>375406.206897593</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>370049.3193683</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>358969.385801263</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>434671.63318928</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>515471.232612165</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>538253.269946463</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>575181.571399028</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>626743.454254061</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2793.87373155808</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2902.01102236582</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3334.93642962954</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4270.72655581943</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5268.98637861863</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5986.16116244376</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6957.63239491821</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8927.23374108946</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9992.98742230427</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9739.20599757084</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9370.93017000342</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10196.6770895881</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9941.35496054454</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10656.753988155</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10555.4785353465</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4002.77836802995</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4388.67803750515</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4484.25212354587</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5648.31433980146</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6872.00064717984</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7107.89849837285</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7397.92431950002</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8682.82239584366</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10175.1355588096</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9318.12266566179</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10036.7329479272</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11209.7777763731</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11452.0343635971</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12112.1571871676</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12883.903814792</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1949.80546074671</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2068.35790147548</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2011.00724912722</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2316.13846256222</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2772.72728991002</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3241.89543588432</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4005.261734758</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5974.1745465886</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7317.17552499112</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6085.68174340788</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6465.13266136164</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7238.47547872084</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7542.28382413765</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7875.6512248432</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7951.49131158792</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>167402.603970982</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180064.651385406</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>183856.637013725</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179342.923118187</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>188274.819230884</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>209203.04273962</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>229244.707619988</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>244448.868163421</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>265504.860030377</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>235395.419560812</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>262304.946133162</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>288434.993826294</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>292999.497955436</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>308170.764767338</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>311932.689424559</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1106.13775198616</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1148.31969136966</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1192.10278820991</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1432.86045473778</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1637.21722068071</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1733.75001641791</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2000.6854906638</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2394.36326444445</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2841.45162892964</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2833.63266979318</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2834.22701336085</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3064.77138852171</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3064.97198752232</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3227.48461346777</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3442.68474147421</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98628.6376512724</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100712.655399886</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109942.368802451</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135061.075511246</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>152031.643711481</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>155546.216502832</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162310.150846214</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>181761.057710401</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>205275.131643774</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>207078.916718495</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>206496.385875124</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>219625.088051712</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>208851.779194848</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>233792.735302118</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>230690.559561229</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25505.5372773167</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27896.1533624624</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29102.1570774225</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32573.7795957501</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35738.3230957667</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40368.9988633374</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43316.6206095945</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54441.4415700064</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66207.6725223462</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54629.6988228424</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60518.036940243</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65474.4110249414</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63294.4668848652</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67899.4751570222</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72670.6897127309</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19805.9373579684</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19963.7947910797</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22265.7405683154</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27377.8134525144</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31192.1790644081</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32347.4410446631</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37666.3564411894</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44638.6644474371</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61441.4897028029</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59607.2562396546</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58486.4490157974</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63012.6164364318</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59583.1973629913</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62686.6574701797</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64662.0537670508</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10709.7814480995</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11867.2069581224</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13144.3735824057</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16476.6458456056</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19951.3956042949</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25599.7102282455</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30526.7670475514</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43141.4790229041</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51478.4927585944</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43890.3736316759</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46701.5730756354</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55369.1182903681</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53433.5558177998</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60924.4951219508</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62627.4792474356</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72410.652190693</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80760.2882142641</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87182.5529060631</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103209.430774678</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132549.787033459</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>155445.532012455</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>187438.566082529</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>247282.397833211</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>307144.516822803</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>262314.957509309</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>316151.193680319</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>371829.458831327</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>396066.593880761</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>407191.885318571</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>360243.057461838</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10825.5872075986</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11997.3344172002</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13675.2298022419</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17797.0562294426</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20787.6766409607</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23140.1873976793</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24586.3924799378</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31206.1377601449</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37172.2329199294</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36486.747950416</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35296.4511982166</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40388.1841585647</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37120.2747053774</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40960.3513101226</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42856.9990720959</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5799.58538524063</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5876.58121073843</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6258.20660450584</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7697.06564143323</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9185.28359517091</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9884.26035153541</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10532.2947667588</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12218.8117158213</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14043.1431421241</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13271.8685097568</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13189.4602282694</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14541.0524324994</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13592.5504154905</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14416.4070353792</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14415.6748058087</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64127.4402060896</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61047.6728271599</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66703.0160419285</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83179.0065339861</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95027.5240765651</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96824.4390250709</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101375.578421036</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116302.110675564</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129996.950042888</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121209.582111301</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132513.975916134</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151494.539206399</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149903.663576712</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>159796.617972194</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154529.735551692</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62801.326267524</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50034.4912795609</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51743.5014864738</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63367.3158880944</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82401.9742799187</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94732.5638092292</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>107056.660295157</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>122127.001655227</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153826.191806676</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140946.223838874</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151104.895023956</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>169439.607988055</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>169833.841858652</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>178059.444491799</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>178389.958587003</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73199.7629399825</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70359.7148834826</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72195.2462762918</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76845.2066869203</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87934.3196206847</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94787.4243865409</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100516.903455041</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109255.542079937</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>124785.877116933</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122716.528866725</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>133999.87061128</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>152278.187363611</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>156970.115090535</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160705.206394109</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>164092.543400601</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.667</t>
+          <t>2667107.52795144</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.773</t>
+          <t>2773982.7545347</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.805</t>
+          <t>2803136.9649619</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.905</t>
+          <t>2902721.7435994</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>3.146</t>
+          <t>3144470.36998675</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3.427</t>
+          <t>3426684.27192057</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>3.758</t>
+          <t>3757234.9798271</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>4.087</t>
+          <t>4083351.47714329</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>4.371</t>
+          <t>4370231.06678095</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>4.427</t>
+          <t>4427831.99968818</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4655786.08530718</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>4.897</t>
+          <t>4890812.4770523</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>5.008</t>
+          <t>5006343.33940849</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>5.138</t>
+          <t>5137153.9664218</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>5.261</t>
+          <t>5263587.24929634</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>781944.362003292</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>776989.344365054</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>765971.325364832</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>876822.096730077</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>1052946.58653483</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1.284</t>
+          <t>1283466.47039423</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1430685.15599202</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1597573.79948083</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>1885221.05623634</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1.772</t>
+          <t>1770782.01170685</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2.131</t>
+          <t>2129205.60093568</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2.469</t>
+          <t>2467475.73005486</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2.604</t>
+          <t>2602486.12832423</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2.596</t>
+          <t>2596470.76078158</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2.581</t>
+          <t>2581890.77681025</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7.847</t>
+          <t>7846223.87592984</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7.883</t>
+          <t>7875336.47864516</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>8113298.99872537</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>9.075</t>
+          <t>9060000.30607258</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10212240.6885657</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>11.179</t>
+          <t>11175012.1341031</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>12.088</t>
+          <t>12090068.6793164</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>13.542</t>
+          <t>13521864.4472986</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>15.266</t>
+          <t>15256973.3726471</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>15.267</t>
+          <t>15273124.0971955</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>16.766</t>
+          <t>16757131.4064602</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18656026.4633716</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>19.178</t>
+          <t>19163619.8626624</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>19.561</t>
+          <t>19561546.4027473</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>20.002</t>
+          <t>20001321.5491715</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4297.37964271068</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4301.58422108436</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4955.20689103708</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6159.04417887557</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7631.69697776228</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8333.09264368812</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9321.3323711031</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11037.5013167068</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13227.6341513467</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12595.8632427103</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12632.6575585243</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13627.4994010128</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12594.5153822829</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13270.2782687269</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13062.8099043145</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86492.9860826985</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87619.0436738162</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92288.9708240197</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108418.019376533</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116214.327563931</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>119816.360820991</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>124525.582961366</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140212.586397603</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165663.864108622</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>167832.992639181</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>173361.169349531</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>205826.765395347</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>199772.844562774</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>204796.049296937</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>209922.235840823</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38828.820366918</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39260.7429726079</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44177.8428514702</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49462.2851379609</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55434.0482412998</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62065.3812219946</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68243.6297937369</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82319.1801557791</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94994.4651759168</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92866.7440816386</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>100016.097560435</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113571.051891685</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114704.425789506</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>120694.928080659</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119371.069537673</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>capital_depreciation.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
